--- a/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2015-16-boys-u11-white.xlsx
+++ b/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2015-16-boys-u11-white.xlsx
@@ -169,7 +169,7 @@
       </c>
       <c r="I2" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2015-16-boys-u11-white.xlsx
+++ b/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2015-16-boys-u11-white.xlsx
@@ -269,17 +269,17 @@
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 24, 2026</t>
+          <t>Sunday, October 25, 2026</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>17:00 EDT</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
         <is>
-          <t>Soccer Stars United Pulsar 2015/2016</t>
+          <t>Soccer Stars United Met Oval - SSU Black 2015/2016 (Formerly Pulsar)</t>
         </is>
       </c>
       <c r="E5" s="0" t="inlineStr">
@@ -294,7 +294,7 @@
       </c>
       <c r="G5" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Randall's Island - 10A - Icahn</t>
         </is>
       </c>
       <c r="H5" s="0" t="inlineStr">
@@ -302,7 +302,11 @@
           <t>U11 (9v9) - D4 City</t>
         </is>
       </c>
-      <c r="I5" s="0"/>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>Scheduled</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">

--- a/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2015-16-boys-u11-white.xlsx
+++ b/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2015-16-boys-u11-white.xlsx
@@ -74,7 +74,7 @@
     <col min="2" max="2" bestFit="1" customWidth="1" width="28.6"/>
     <col min="3" max="3" bestFit="1" customWidth="1" width="13.200000000000001"/>
     <col min="4" max="4" bestFit="1" customWidth="1" width="50.6"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" width="6.6000000000000005"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" width="7.700000000000001"/>
     <col min="6" max="6" bestFit="1" customWidth="1" width="50.6"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="55.00000000000001"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="18.700000000000003"/>
@@ -194,7 +194,7 @@
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 - 2</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2015-16-boys-u11-white.xlsx
+++ b/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2015-16-boys-u11-white.xlsx
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 - 9</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">

--- a/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2015-16-boys-u11-white.xlsx
+++ b/data/2026/cjsl/fall/metropolitan-oval-academy-brooklyn-2015-16-boys-u11-white.xlsx
@@ -284,7 +284,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 - 3</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
